--- a/Pruebas calificadas/COLEGIO LUIS LOPEZ DE MESA IED-1101_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO LUIS LOPEZ DE MESA IED-1101_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -1056,11 +1052,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -1309,11 +1301,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -1562,11 +1550,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -1815,11 +1799,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -2068,11 +2048,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -2321,11 +2297,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -2574,11 +2546,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -2827,11 +2795,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -3080,11 +3044,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -3333,11 +3293,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -3586,11 +3542,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -3839,11 +3791,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -4092,11 +4040,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -4345,11 +4289,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -4598,11 +4538,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -4851,11 +4787,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -5104,11 +5036,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -5357,11 +5285,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -5610,11 +5534,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -5863,11 +5783,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -6116,11 +6032,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -6369,11 +6281,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -6622,11 +6530,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -6875,11 +6779,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -7128,11 +7028,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -7381,11 +7277,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -7634,11 +7526,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -7887,11 +7775,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -8140,11 +8024,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -8393,11 +8273,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -8646,11 +8522,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -8899,11 +8771,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -9152,11 +9020,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -9405,11 +9269,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -9658,11 +9518,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -9911,11 +9767,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -10164,11 +10016,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -10417,11 +10265,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -10670,11 +10514,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -10923,11 +10763,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -11176,11 +11012,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -11429,11 +11261,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -11682,11 +11510,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -11935,11 +11759,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -12188,11 +12008,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -12441,11 +12257,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -12694,11 +12506,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -12947,11 +12755,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -13200,11 +13004,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -13445,11 +13245,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -13698,11 +13494,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -13951,11 +13743,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -14196,11 +13984,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -14449,11 +14233,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -14702,11 +14482,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -14955,11 +14731,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -15208,11 +14980,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -15461,11 +15229,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
@@ -15714,11 +15478,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111102000265</t>
